--- a/test/fixtures/timetrackers/clean.xlsx
+++ b/test/fixtures/timetrackers/clean.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="TimeTracker" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Time" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="112">
   <si>
     <t>Employee Name</t>
   </si>
@@ -22,15 +22,9 @@
     <t>Time Tracker Start Date</t>
   </si>
   <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
     <t>Time Tracker End Date</t>
   </si>
   <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -52,56 +46,326 @@
     <t>Duration</t>
   </si>
   <si>
+    <t>Time Range</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
+    <t>James F. Kimmel &amp; Associates</t>
+  </si>
+  <si>
+    <t>Tax Return Preparation</t>
+  </si>
+  <si>
     <t>Acme Corp</t>
   </si>
   <si>
-    <t>Tax Compliance</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>Prepared 1040 individual return — reviewed Schedule A and B</t>
+    <t>8:00-8:15</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 1)</t>
+  </si>
+  <si>
+    <t>Monthly Services</t>
   </si>
   <si>
     <t>Globex Industries</t>
   </si>
   <si>
-    <t>Bookkeeping</t>
-  </si>
-  <si>
-    <t>Monthly bookkeeping reconciliation — bank and credit card accounts</t>
-  </si>
-  <si>
-    <t>Smith, John</t>
-  </si>
-  <si>
-    <t>Consulting</t>
-  </si>
-  <si>
-    <t>Client consultation on tax projection for next quarter</t>
-  </si>
-  <si>
-    <t>Smith, Jane</t>
-  </si>
-  <si>
-    <t>Wayne Enterprises</t>
+    <t>8:15-8:45</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 2)</t>
+  </si>
+  <si>
+    <t>Phone Call</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>8:45-9:30</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 3)</t>
+  </si>
+  <si>
+    <t>9:30-10:30</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 4)</t>
+  </si>
+  <si>
+    <t>10:30-12:00</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 5)</t>
+  </si>
+  <si>
+    <t>12:00-12:15</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 6)</t>
+  </si>
+  <si>
+    <t>12:15-12:45</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 7)</t>
+  </si>
+  <si>
+    <t>12:45-13:30</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 8)</t>
+  </si>
+  <si>
+    <t>13:30-14:30</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 9)</t>
+  </si>
+  <si>
+    <t>8:00-9:30</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 10)</t>
+  </si>
+  <si>
+    <t>9:30-9:45</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 11)</t>
+  </si>
+  <si>
+    <t>9:45-10:15</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 12)</t>
+  </si>
+  <si>
+    <t>10:15-11:00</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 13)</t>
+  </si>
+  <si>
+    <t>11:00-12:00</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 14)</t>
+  </si>
+  <si>
+    <t>12:00-13:30</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 15)</t>
+  </si>
+  <si>
+    <t>13:30-13:45</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 16)</t>
+  </si>
+  <si>
+    <t>13:45-14:15</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 17)</t>
+  </si>
+  <si>
+    <t>14:15-15:00</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 18)</t>
+  </si>
+  <si>
+    <t>8:00-9:00</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 19)</t>
+  </si>
+  <si>
+    <t>9:00-10:30</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 20)</t>
+  </si>
+  <si>
+    <t>10:30-10:45</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 21)</t>
+  </si>
+  <si>
+    <t>10:45-11:15</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 22)</t>
+  </si>
+  <si>
+    <t>11:15-12:00</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 23)</t>
+  </si>
+  <si>
+    <t>12:00-13:00</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 24)</t>
+  </si>
+  <si>
+    <t>13:00-14:30</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 25)</t>
+  </si>
+  <si>
+    <t>14:30-14:45</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 26)</t>
+  </si>
+  <si>
+    <t>14:45-15:15</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 27)</t>
+  </si>
+  <si>
+    <t>8:00-8:45</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 28)</t>
+  </si>
+  <si>
+    <t>8:45-9:45</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 29)</t>
+  </si>
+  <si>
+    <t>9:45-11:15</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 30)</t>
+  </si>
+  <si>
+    <t>11:15-11:30</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 31)</t>
+  </si>
+  <si>
+    <t>11:30-12:00</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 32)</t>
+  </si>
+  <si>
+    <t>12:00-12:45</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 33)</t>
+  </si>
+  <si>
+    <t>12:45-13:45</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 34)</t>
+  </si>
+  <si>
+    <t>13:45-15:15</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 35)</t>
+  </si>
+  <si>
+    <t>15:15-15:30</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 36)</t>
+  </si>
+  <si>
+    <t>8:00-8:30</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 37)</t>
+  </si>
+  <si>
+    <t>8:30-9:15</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 38)</t>
+  </si>
+  <si>
+    <t>9:15-10:15</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 39)</t>
+  </si>
+  <si>
+    <t>10:15-11:45</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 40)</t>
+  </si>
+  <si>
+    <t>11:45-12:00</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 41)</t>
+  </si>
+  <si>
+    <t>12:00-12:30</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 42)</t>
+  </si>
+  <si>
+    <t>12:30-13:15</t>
+  </si>
+  <si>
+    <t>Prepared 1040 individual return and reviewed Schedule A and B (item 43)</t>
+  </si>
+  <si>
+    <t>13:15-14:15</t>
+  </si>
+  <si>
+    <t>Monthly bookkeeping reconciliation for bank and credit card accounts (item 44)</t>
+  </si>
+  <si>
+    <t>14:15-15:45</t>
+  </si>
+  <si>
+    <t>Client consultation on the tax projection for next quarter (item 45)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -124,8 +388,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -480,59 +746,59 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2">
+        <v>46139</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
+      <c r="A6" s="2">
+        <v>46139</v>
       </c>
       <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
       <c r="D6" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
@@ -540,28 +806,28 @@
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>60</v>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
+      <c r="A7" s="2">
+        <v>46139</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
@@ -569,57 +835,57 @@
       <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7">
-        <v>75</v>
+      <c r="G7">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
+      <c r="A8" s="2">
+        <v>46139</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8">
-        <v>90</v>
+        <v>25</v>
+      </c>
+      <c r="G8">
+        <v>45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
+      <c r="A9" s="2">
+        <v>46139</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
@@ -627,28 +893,28 @@
       <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="G9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9">
-        <v>105</v>
+      <c r="G9">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
+      <c r="A10" s="2">
+        <v>46139</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
@@ -656,57 +922,57 @@
       <c r="F10" t="s">
         <v>16</v>
       </c>
-      <c r="G10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10">
-        <v>120</v>
+      <c r="G10">
+        <v>90</v>
+      </c>
+      <c r="H10" t="s">
+        <v>30</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
+      <c r="A11" s="2">
+        <v>46139</v>
       </c>
       <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11">
-        <v>60</v>
-      </c>
-      <c r="I11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
       <c r="D12" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
@@ -714,28 +980,28 @@
       <c r="F12" t="s">
         <v>16</v>
       </c>
-      <c r="G12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12">
-        <v>75</v>
+      <c r="G12">
+        <v>30</v>
+      </c>
+      <c r="H12" t="s">
+        <v>34</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
+      <c r="A13" s="2">
+        <v>46139</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
@@ -743,86 +1009,86 @@
       <c r="F13" t="s">
         <v>16</v>
       </c>
-      <c r="G13" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13">
+      <c r="G13">
+        <v>45</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14">
+        <v>60</v>
+      </c>
+      <c r="H14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>46140</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15">
         <v>90</v>
       </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14">
-        <v>105</v>
-      </c>
-      <c r="I14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15">
-        <v>120</v>
+      <c r="H15" t="s">
+        <v>40</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>3</v>
+      <c r="A16" s="2">
+        <v>46140</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
         <v>16</v>
@@ -830,57 +1096,57 @@
       <c r="F16" t="s">
         <v>16</v>
       </c>
-      <c r="G16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16">
-        <v>60</v>
+      <c r="G16">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>42</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>3</v>
+      <c r="A17" s="2">
+        <v>46140</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17">
-        <v>75</v>
+        <v>25</v>
+      </c>
+      <c r="G17">
+        <v>30</v>
+      </c>
+      <c r="H17" t="s">
+        <v>44</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>3</v>
+      <c r="A18" s="2">
+        <v>46140</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
@@ -888,28 +1154,28 @@
       <c r="F18" t="s">
         <v>16</v>
       </c>
-      <c r="G18" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18">
-        <v>90</v>
+      <c r="G18">
+        <v>45</v>
+      </c>
+      <c r="H18" t="s">
+        <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>3</v>
+      <c r="A19" s="2">
+        <v>46140</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
         <v>16</v>
@@ -917,57 +1183,57 @@
       <c r="F19" t="s">
         <v>16</v>
       </c>
-      <c r="G19" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19">
-        <v>105</v>
+      <c r="G19">
+        <v>60</v>
+      </c>
+      <c r="H19" t="s">
+        <v>48</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>3</v>
+      <c r="A20" s="2">
+        <v>46140</v>
       </c>
       <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" t="s">
         <v>25</v>
       </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20">
-        <v>120</v>
+      <c r="G20">
+        <v>90</v>
+      </c>
+      <c r="H20" t="s">
+        <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>3</v>
+      <c r="A21" s="2">
+        <v>46140</v>
       </c>
       <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
         <v>14</v>
       </c>
-      <c r="C21" t="s">
-        <v>15</v>
-      </c>
       <c r="D21" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
@@ -975,28 +1241,28 @@
       <c r="F21" t="s">
         <v>16</v>
       </c>
-      <c r="G21" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21">
-        <v>60</v>
+      <c r="G21">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
+        <v>52</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>3</v>
+      <c r="A22" s="2">
+        <v>46140</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E22" t="s">
         <v>16</v>
@@ -1004,57 +1270,57 @@
       <c r="F22" t="s">
         <v>16</v>
       </c>
-      <c r="G22" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22">
-        <v>75</v>
+      <c r="G22">
+        <v>30</v>
+      </c>
+      <c r="H22" t="s">
+        <v>54</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>3</v>
+      <c r="A23" s="2">
+        <v>46140</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23">
-        <v>90</v>
+        <v>25</v>
+      </c>
+      <c r="G23">
+        <v>45</v>
+      </c>
+      <c r="H23" t="s">
+        <v>56</v>
       </c>
       <c r="I23" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>3</v>
+      <c r="A24" s="2">
+        <v>46141</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
         <v>16</v>
@@ -1062,28 +1328,28 @@
       <c r="F24" t="s">
         <v>16</v>
       </c>
-      <c r="G24" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24">
-        <v>105</v>
+      <c r="G24">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
+        <v>58</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>3</v>
+      <c r="A25" s="2">
+        <v>46141</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E25" t="s">
         <v>16</v>
@@ -1091,57 +1357,57 @@
       <c r="F25" t="s">
         <v>16</v>
       </c>
-      <c r="G25" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25">
-        <v>120</v>
+      <c r="G25">
+        <v>90</v>
+      </c>
+      <c r="H25" t="s">
+        <v>60</v>
       </c>
       <c r="I25" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>3</v>
+      <c r="A26" s="2">
+        <v>46141</v>
       </c>
       <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
         <v>14</v>
       </c>
-      <c r="C26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" t="s">
-        <v>16</v>
-      </c>
-      <c r="H26">
-        <v>60</v>
-      </c>
-      <c r="I26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
       <c r="D27" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
         <v>16</v>
@@ -1149,28 +1415,28 @@
       <c r="F27" t="s">
         <v>16</v>
       </c>
-      <c r="G27" t="s">
-        <v>16</v>
-      </c>
-      <c r="H27">
-        <v>75</v>
+      <c r="G27">
+        <v>30</v>
+      </c>
+      <c r="H27" t="s">
+        <v>64</v>
       </c>
       <c r="I27" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>3</v>
+      <c r="A28" s="2">
+        <v>46141</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
         <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
         <v>16</v>
@@ -1178,86 +1444,86 @@
       <c r="F28" t="s">
         <v>16</v>
       </c>
-      <c r="G28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28">
+      <c r="G28">
+        <v>45</v>
+      </c>
+      <c r="H28" t="s">
+        <v>66</v>
+      </c>
+      <c r="I28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29">
+        <v>60</v>
+      </c>
+      <c r="H29" t="s">
+        <v>68</v>
+      </c>
+      <c r="I29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30">
         <v>90</v>
       </c>
-      <c r="I28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29">
-        <v>105</v>
-      </c>
-      <c r="I29" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" t="s">
-        <v>16</v>
-      </c>
-      <c r="G30" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30">
-        <v>120</v>
+      <c r="H30" t="s">
+        <v>70</v>
       </c>
       <c r="I30" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>3</v>
+      <c r="A31" s="2">
+        <v>46141</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
         <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
         <v>16</v>
@@ -1265,57 +1531,57 @@
       <c r="F31" t="s">
         <v>16</v>
       </c>
-      <c r="G31" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31">
-        <v>60</v>
+      <c r="G31">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>72</v>
       </c>
       <c r="I31" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>3</v>
+      <c r="A32" s="2">
+        <v>46141</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H32">
+        <v>25</v>
+      </c>
+      <c r="G32">
+        <v>30</v>
+      </c>
+      <c r="H32" t="s">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s">
         <v>75</v>
       </c>
-      <c r="I32" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>3</v>
+      <c r="A33" s="2">
+        <v>46142</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
         <v>16</v>
@@ -1323,28 +1589,28 @@
       <c r="F33" t="s">
         <v>16</v>
       </c>
-      <c r="G33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33">
-        <v>90</v>
+      <c r="G33">
+        <v>45</v>
+      </c>
+      <c r="H33" t="s">
+        <v>76</v>
       </c>
       <c r="I33" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>3</v>
+      <c r="A34" s="2">
+        <v>46142</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
         <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E34" t="s">
         <v>16</v>
@@ -1352,57 +1618,57 @@
       <c r="F34" t="s">
         <v>16</v>
       </c>
-      <c r="G34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H34">
-        <v>105</v>
+      <c r="G34">
+        <v>60</v>
+      </c>
+      <c r="H34" t="s">
+        <v>78</v>
       </c>
       <c r="I34" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>3</v>
+      <c r="A35" s="2">
+        <v>46142</v>
       </c>
       <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" t="s">
         <v>25</v>
       </c>
-      <c r="C35" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" t="s">
-        <v>16</v>
-      </c>
-      <c r="G35" t="s">
-        <v>16</v>
-      </c>
-      <c r="H35">
-        <v>120</v>
+      <c r="G35">
+        <v>90</v>
+      </c>
+      <c r="H35" t="s">
+        <v>80</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>3</v>
+      <c r="A36" s="2">
+        <v>46142</v>
       </c>
       <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" t="s">
         <v>14</v>
       </c>
-      <c r="C36" t="s">
-        <v>15</v>
-      </c>
       <c r="D36" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
         <v>16</v>
@@ -1410,28 +1676,28 @@
       <c r="F36" t="s">
         <v>16</v>
       </c>
-      <c r="G36" t="s">
-        <v>16</v>
-      </c>
-      <c r="H36">
-        <v>60</v>
+      <c r="G36">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>82</v>
       </c>
       <c r="I36" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>3</v>
+      <c r="A37" s="2">
+        <v>46142</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
       </c>
       <c r="D37" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E37" t="s">
         <v>16</v>
@@ -1439,57 +1705,57 @@
       <c r="F37" t="s">
         <v>16</v>
       </c>
-      <c r="G37" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37">
-        <v>75</v>
+      <c r="G37">
+        <v>30</v>
+      </c>
+      <c r="H37" t="s">
+        <v>84</v>
       </c>
       <c r="I37" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>3</v>
+      <c r="A38" s="2">
+        <v>46142</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D38" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38">
-        <v>90</v>
+        <v>25</v>
+      </c>
+      <c r="G38">
+        <v>45</v>
+      </c>
+      <c r="H38" t="s">
+        <v>86</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>3</v>
+      <c r="A39" s="2">
+        <v>46142</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E39" t="s">
         <v>16</v>
@@ -1497,28 +1763,28 @@
       <c r="F39" t="s">
         <v>16</v>
       </c>
-      <c r="G39" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39">
-        <v>105</v>
+      <c r="G39">
+        <v>60</v>
+      </c>
+      <c r="H39" t="s">
+        <v>88</v>
       </c>
       <c r="I39" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>3</v>
+      <c r="A40" s="2">
+        <v>46142</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E40" t="s">
         <v>16</v>
@@ -1526,57 +1792,57 @@
       <c r="F40" t="s">
         <v>16</v>
       </c>
-      <c r="G40" t="s">
-        <v>16</v>
-      </c>
-      <c r="H40">
-        <v>120</v>
+      <c r="G40">
+        <v>90</v>
+      </c>
+      <c r="H40" t="s">
+        <v>90</v>
       </c>
       <c r="I40" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>3</v>
+      <c r="A41" s="2">
+        <v>46142</v>
       </c>
       <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41">
+        <v>15</v>
+      </c>
+      <c r="H41" t="s">
+        <v>92</v>
+      </c>
+      <c r="I41" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
         <v>14</v>
       </c>
-      <c r="C41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D41" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
-        <v>16</v>
-      </c>
-      <c r="F41" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41" t="s">
-        <v>16</v>
-      </c>
-      <c r="H41">
-        <v>60</v>
-      </c>
-      <c r="I41" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" t="s">
-        <v>15</v>
-      </c>
       <c r="D42" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
         <v>16</v>
@@ -1584,28 +1850,28 @@
       <c r="F42" t="s">
         <v>16</v>
       </c>
-      <c r="G42" t="s">
-        <v>16</v>
-      </c>
-      <c r="H42">
-        <v>75</v>
+      <c r="G42">
+        <v>30</v>
+      </c>
+      <c r="H42" t="s">
+        <v>94</v>
       </c>
       <c r="I42" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>3</v>
+      <c r="A43" s="2">
+        <v>46143</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
         <v>19</v>
       </c>
       <c r="D43" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E43" t="s">
         <v>16</v>
@@ -1613,86 +1879,86 @@
       <c r="F43" t="s">
         <v>16</v>
       </c>
-      <c r="G43" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43">
+      <c r="G43">
+        <v>45</v>
+      </c>
+      <c r="H43" t="s">
+        <v>96</v>
+      </c>
+      <c r="I43" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44">
+        <v>60</v>
+      </c>
+      <c r="H44" t="s">
+        <v>98</v>
+      </c>
+      <c r="I44" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45">
         <v>90</v>
       </c>
-      <c r="I43" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>16</v>
-      </c>
-      <c r="F44" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" t="s">
-        <v>16</v>
-      </c>
-      <c r="H44">
-        <v>105</v>
-      </c>
-      <c r="I44" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>3</v>
-      </c>
-      <c r="B45" t="s">
-        <v>25</v>
-      </c>
-      <c r="C45" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" t="s">
-        <v>16</v>
-      </c>
-      <c r="F45" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45">
-        <v>120</v>
+      <c r="H45" t="s">
+        <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>3</v>
+      <c r="A46" s="2">
+        <v>46143</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
         <v>19</v>
       </c>
       <c r="D46" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E46" t="s">
         <v>16</v>
@@ -1700,57 +1966,57 @@
       <c r="F46" t="s">
         <v>16</v>
       </c>
-      <c r="G46" t="s">
-        <v>16</v>
-      </c>
-      <c r="H46">
-        <v>60</v>
+      <c r="G46">
+        <v>15</v>
+      </c>
+      <c r="H46" t="s">
+        <v>102</v>
       </c>
       <c r="I46" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>3</v>
+      <c r="A47" s="2">
+        <v>46143</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" t="s">
-        <v>16</v>
-      </c>
-      <c r="H47">
-        <v>75</v>
+        <v>25</v>
+      </c>
+      <c r="G47">
+        <v>30</v>
+      </c>
+      <c r="H47" t="s">
+        <v>104</v>
       </c>
       <c r="I47" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>3</v>
+      <c r="A48" s="2">
+        <v>46143</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
         <v>16</v>
@@ -1758,28 +2024,28 @@
       <c r="F48" t="s">
         <v>16</v>
       </c>
-      <c r="G48" t="s">
-        <v>16</v>
-      </c>
-      <c r="H48">
-        <v>90</v>
+      <c r="G48">
+        <v>45</v>
+      </c>
+      <c r="H48" t="s">
+        <v>106</v>
       </c>
       <c r="I48" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>3</v>
+      <c r="A49" s="2">
+        <v>46143</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
         <v>19</v>
       </c>
       <c r="D49" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E49" t="s">
         <v>16</v>
@@ -1787,188 +2053,43 @@
       <c r="F49" t="s">
         <v>16</v>
       </c>
-      <c r="G49" t="s">
-        <v>16</v>
-      </c>
-      <c r="H49">
-        <v>105</v>
+      <c r="G49">
+        <v>60</v>
+      </c>
+      <c r="H49" t="s">
+        <v>108</v>
       </c>
       <c r="I49" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>3</v>
+      <c r="A50" s="2">
+        <v>46143</v>
       </c>
       <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" t="s">
         <v>25</v>
       </c>
-      <c r="C50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" t="s">
-        <v>16</v>
-      </c>
-      <c r="G50" t="s">
-        <v>16</v>
-      </c>
-      <c r="H50">
-        <v>120</v>
+      <c r="G50">
+        <v>90</v>
+      </c>
+      <c r="H50" t="s">
+        <v>110</v>
       </c>
       <c r="I50" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>3</v>
-      </c>
-      <c r="B51" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" t="s">
-        <v>15</v>
-      </c>
-      <c r="D51" t="s">
-        <v>1</v>
-      </c>
-      <c r="E51" t="s">
-        <v>16</v>
-      </c>
-      <c r="F51" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51" t="s">
-        <v>16</v>
-      </c>
-      <c r="H51">
-        <v>60</v>
-      </c>
-      <c r="I51" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>3</v>
-      </c>
-      <c r="B52" t="s">
-        <v>18</v>
-      </c>
-      <c r="C52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" t="s">
-        <v>16</v>
-      </c>
-      <c r="F52" t="s">
-        <v>16</v>
-      </c>
-      <c r="G52" t="s">
-        <v>16</v>
-      </c>
-      <c r="H52">
-        <v>75</v>
-      </c>
-      <c r="I52" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>3</v>
-      </c>
-      <c r="B53" t="s">
-        <v>21</v>
-      </c>
-      <c r="C53" t="s">
-        <v>22</v>
-      </c>
-      <c r="D53" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" t="s">
-        <v>16</v>
-      </c>
-      <c r="F53" t="s">
-        <v>16</v>
-      </c>
-      <c r="G53" t="s">
-        <v>16</v>
-      </c>
-      <c r="H53">
-        <v>90</v>
-      </c>
-      <c r="I53" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>3</v>
-      </c>
-      <c r="B54" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" t="s">
-        <v>16</v>
-      </c>
-      <c r="F54" t="s">
-        <v>16</v>
-      </c>
-      <c r="G54" t="s">
-        <v>16</v>
-      </c>
-      <c r="H54">
-        <v>105</v>
-      </c>
-      <c r="I54" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>3</v>
-      </c>
-      <c r="B55" t="s">
-        <v>25</v>
-      </c>
-      <c r="C55" t="s">
-        <v>19</v>
-      </c>
-      <c r="D55" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
-        <v>16</v>
-      </c>
-      <c r="F55" t="s">
-        <v>16</v>
-      </c>
-      <c r="G55" t="s">
-        <v>16</v>
-      </c>
-      <c r="H55">
-        <v>120</v>
-      </c>
-      <c r="I55" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
